--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（806段落130表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（843段落137表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（843段落137表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（926段落145表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（926段落145表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（928段落145表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（928段落145表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（951段落146表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（951段落146表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（973段落148表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（973段落148表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（999段落151表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（999段落151表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（1024段落152表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（1024段落152表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（1027段落153表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（1027段落153表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（1030段落153表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（1030段落153表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（1038段落153表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（1038段落153表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（1060段落156表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（1060段落156表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（1059段落156表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（1059段落156表36図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（1062段落156表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
